--- a/data/daily/2026-09/2026-09-23.xlsx
+++ b/data/daily/2026-09/2026-09-23.xlsx
@@ -1195,14 +1195,39 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="381000" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>3</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="342900" cy="457200"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="2" name="Image 2" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId2"/>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1217,17 +1242,17 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>3</row>
+      <row>4</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="342900" cy="457200"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="3" name="Image 3" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId3"/>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1242,17 +1267,17 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>4</row>
+      <row>5</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="342900" cy="457200"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="4" name="Image 4" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId4"/>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1267,85 +1292,60 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>5</row>
+      <row>6</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="342900" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>7</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="342900" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>8</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="5" name="Image 5" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>6</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="342900" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="6" name="Image 6" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>7</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="342900" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="7" name="Image 7" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>8</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="342900" cy="457200"/>
     <pic>
       <nvPicPr>
         <cNvPr id="8" name="Image 8" descr="Picture"/>
@@ -1450,27 +1450,52 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="1028700" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="933450" cy="1238250"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="2" name="Image 2" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>4</col>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>5</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
@@ -1478,24 +1503,24 @@
     <ext cx="933450" cy="1238250"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="3" name="Image 3" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
@@ -1503,104 +1528,79 @@
     <ext cx="933450" cy="1238250"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="4" name="Image 4" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>6</col>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="933450" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="933450" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="1028700" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="5" name="Image 5" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>7</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="933450" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="6" name="Image 6" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>8</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="933450" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="7" name="Image 7" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>9</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="933450" cy="1238250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="8" name="Image 8" descr="Picture"/>
@@ -2596,27 +2596,31 @@
         <v>4</v>
       </c>
       <c r="J2" t="n">
-        <v>16117</v>
+        <v>16119</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>훌륭한 선물용 패키지 — 포장 상태가 깔끔하고 품격 있어 선물용으로 주고받기 좋음</t>
+          <t>피로 회복 및 활력 충전 — 섭취 후 피로가 풀리고 컨디션 회복에 도움됨</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>우수한 피로 회복 효과 — 섭취 후 체력이 회복되고 몸의 변화가 뚜렷하게 체감됨</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr"/>
+          <t>선물용 높은 만족도 — 고급 비타민 이미지로 가볍게 선물하거나 받기에 좋음</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>정돈된 꼼꼼한 포장 — 배송 시 제품 포장이 깔끔하게 정돈되어 도착함</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>포장 구성품 누락 — 선물용 에디션임에도 쇼핑백이 동봉되지 않아 개별 구매가 필요함</t>
+          <t>쇼핑백 별도 구매 불편 — 기프트 에디션임에도 쇼핑백이 동봉되지 않아 따로 구매해야 함</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>배송 중 박스 훼손 — 배송 도중 상자가 군데군데 찌그러진 상태로 수령됨</t>
+          <t>박스 파손 및 적은 용량 — 외관 상자가 찌그러져 오거나 8일분 용량이 맛보기 수준으로 아쉬움</t>
         </is>
       </c>
       <c r="P2" t="inlineStr"/>
@@ -2659,22 +2663,26 @@
         <v>4</v>
       </c>
       <c r="J3" t="n">
-        <v>15448</v>
+        <v>15450</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>편리한 휴대와 섭취 — 액상 제형으로 한 포씩 챙겨 먹기 편해 일상에서 손이 자주 감</t>
+          <t>편리한 액상형 섭취 — 액상 제형이라 챙겨 먹기 편하고 손이 자주 감</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>기분 좋은 활력 충전 — 복용 후 피로가 풀리고 활력이 생기는 데 도움을 줌</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
+          <t>선물용 고급 패키지 — 포장이 고급스러워 생일이나 응원 선물로 받기 좋음</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>피로 개선 및 기력 회복 — 복용 후 활력이 생기고 피로 회복에 도움됨</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>다소 늦어진 배송 — 배송 완료까지 다소 많은 시일이 소요되어 아쉬움</t>
+          <t>다소 느린 배송 속도 — 주문 후 배송이 늦게 도착함</t>
         </is>
       </c>
       <c r="O3" t="inlineStr"/>
@@ -2722,18 +2730,22 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>확실한 컨디션 회복 — 섭취 후 기력이 약해진 상태나 피로감이 눈에 띄게 완화됨</t>
+          <t>뛰어난 피로 회복 효과 — 섭취 후 피로감이 줄고 일상 활력 증진에 도움됨</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>고급스러운 케이스 포장 — 명절 분위기에 어울리는 화사하고 예쁜 케이스에 담겨서 옴</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr"/>
+          <t>고급스러운 명절 선물 — 패키지가 예쁘고 고급스러워 추석이나 생일 선물용으로 적합함</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>합리적인 가격 구성 — 대용량 구성 대비 좋은 가격대로 구매 가능함</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>동봉된 쇼핑백 불량 — 함께 제공된 선물용 가방이 파손된 채 배송되어 온전한 사용이 불가능함</t>
+          <t>쇼핑백 불량 및 파손 — 동봉된 쇼핑백 상태가 불량하여 선물용 전달에 불편함 발생</t>
         </is>
       </c>
       <c r="O4" t="inlineStr"/>
@@ -2777,22 +2789,26 @@
         <v>4</v>
       </c>
       <c r="J5" t="n">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>실용적인 포장 방식 — 개별 포장되어 있어 가방이나 사무실 책상에 보관하며 챙기기 용이함</t>
+          <t>즉각적인 활력 충전 — 섭취 시 힘이 나고 피로 회복에 빠른 체감 효과 있음</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>빠른 에너지 보충 — 힘든 일정 시작 전 복용 시 기력 충전에 실질적인 도움을 줌</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
+          <t>간편한 개별 포장 휴대 — 한 포씩 개별 포장되어 가방이나 책상에 두고 챙기기 용이함</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>선물용 고급스러운 외관 — 포장 상태가 좋고 고급스러워 지인 선물로 만족스러움</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>배송 요청사항 미반영 — 부재 시 관리실 위탁을 요청하였으나 문 앞에 두고 가 아쉬움이 남음</t>
+          <t>배송 요청사항 미반영 — 부재 시 관리실 위탁 요청이 반영되지 않고 문 앞에 두고 감</t>
         </is>
       </c>
       <c r="O5" t="inlineStr"/>
@@ -2840,15 +2856,19 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>뛰어난 활력 증진 효과 — 섭취 당일의 활력과 전반적인 신체 컨디션 증진에 탁월함</t>
+          <t>피로 회복 및 컨디션 향상 — 복용 후 피로가 풀리고 하루 활력 유지에 뛰어남</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>선물하기 최적화된 포장 — 추가 종이 쇼핑백이 동봉되어 정성 가득한 선물용으로 아주 적합함</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
+          <t>휴대 및 섭취 편의성 — 여행이나 일상에서 한 병씩 들고 다니며 챙겨 먹기 편함</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>쇼핑백 동봉 깔끔한 포장 — 종이봉투가 동봉되어 깔끔하게 선물하거나 전달하기 좋음</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
@@ -2895,15 +2915,19 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>체감되는 기력 충전 — 저녁 섭취 시 활력이 넘쳐 수면을 이루기 힘들 정도로 에너지 충전 효과가 강함</t>
+          <t>즉각적인 활력 및 기운 — 섭취 후 급한 피로가 풀리고 눈에 띄게 힘이 남</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>풍성한 서비스 증정 — 본품 외에 추가 증정품 혜택이 있어 기분 좋게 섭취할 수 있음</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr"/>
+          <t>푸짐한 추가 증정 혜택 — 서비스 추가 증정 구성이 포함되어 만족도가 높음</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>선물에 적합한 예쁜 포장 — 포장이 꼼꼼하고 예뻐 생일이나 위시리스트 선물용으로 적합함</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
@@ -2950,15 +2974,19 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>부담 없는 젤리 제형 — 물 없이 가볍게 씹어서 삼키는 구미 타입이라 섭취 과정이 매우 간편함</t>
+          <t>맛있는 젤리 제형 — 마이구미처럼 달콤하고 맛있어 거부감 없이 섭취 가능</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>거부감 없는 달콤한 맛 — 특유의 비린 향이 전혀 없고 익숙한 과일 맛 젤리 같아 꾸준히 챙기기 좋음</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr"/>
+          <t>물 없는 간편한 섭취 — 물이 필요 없어 출근 전이나 일상에서 간편하게 복용함</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>귀엽고 깔끔한 패키지 — 포장이 깔끔하고 키캡 증정 등 가볍게 선물하기 적합함</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
@@ -3005,20 +3033,20 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>간편한 복용 타입 — 액상과 분말이 결합한 형태로 별도의 물 없이 편리하게 즉각 복용 가능함</t>
+          <t>정관장 브랜드 신뢰도 — 정관장 브랜드 제품이라 성분과 품질을 믿고 섭취함</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>신뢰할 수 있는 브랜드 — 정관장 브랜드 명성에 걸맞은 세련된 포장과 입증된 효능으로 높은 만족감을 줌</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>늦은 시간 섭취 시 각성 — 늦은 저녁에 복용할 경우 강한 각성 작용으로 인해 밤을 새울 우려가 있음</t>
-        </is>
-      </c>
+          <t>올인원 간편 섭취 — 액상과 분말이 함께 있어 물 없이 하루 한 병 섭취 용이함</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>뚜렷한 에너지 보충 효과 — 피곤할 때 마시면 밤잠을 설칠 정도로 기력 보충에 도움됨</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
     </row>
@@ -3064,18 +3092,22 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>피로 감소 및 면역 관리 — 꾸준히 복용할 시 피로감이 줄고 컨디션 유지 및 관리에 상당한 보탬이 됨</t>
+          <t>성별 맞춤 영양 설계 — 성별에 맞춰 m/f 선택이 가능하고 풍부한 영양소 함유</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>맞춤형 맞춤 설계 구성 — 성별 맞춤형 바이탈 옵션을 별도로 지정해 먹을 수 있어 실용적임</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr"/>
+          <t>지속적인 피로 개선 — 꾸준히 복용 시 피로감이 줄고 반짝이는 기운이 유지됨</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>정성 가득한 패키지 — 포장이 깔끔하여 성의 있는 선물로 제격임</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>다소 부담스러운 제제 — 기존 제품들에 비해 알약의 물리적 크기가 커 목넘김에 다소 어려움이 있음</t>
+          <t>부담스러운 정제 크기 — 기존 제품 대비 알약 크기가 커서 삼키기 다소 힘듦</t>
         </is>
       </c>
       <c r="O10" t="inlineStr"/>
@@ -3123,18 +3155,22 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>간편한 아침 건강 챙김 — 액상과 정제를 한 번에 섭취 가능한 편리한 디자인으로 아침 대용으로 훌륭함</t>
+          <t>빠른 피로 회복 체감 — 섭취 시 피로 회복이 빠르고 컨디션 유지에 좋음</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>매우 정성스러운 패키지 — 선물 상자 자체에 신경을 많이 쓴 티가 날 정도로 튼튼하고 고급스러움</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr"/>
+          <t>간편한 복합 제형 섭취 — 액상과 정제를 한 번에 섭취할 수 있어 바쁜 일상에 간편함</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>넉넉한 30일분 구성 — 합리적인 가격에 30일분 대용량이라 장기 관리에 유용함</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>밀봉 씰 및 패키지 오염 — 밀봉 테이프가 여러 번 뗐다 붙인 듯 훼손되어 있고 상자 표면에 손자국과 먼지가 묻어 있음</t>
+          <t>봉인 씰 훼손 및 오염 — 밀봉 스티커가 떼어졌다 붙은 흔적과 손자국 등 이물질이 묻어 있음</t>
         </is>
       </c>
       <c r="O11" t="inlineStr"/>
@@ -3182,18 +3218,22 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>우아한 보자기 선물 포장 — 보자기와 틴케이스를 결합한 화려한 비주얼로 개봉 시 깊은 만족을 선사함</t>
+          <t>고급스러운 보자기 포장 — 틴케이스와 보자기, 쇼핑백 등 선물 포장이 매우 정성스러움</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>비리지 않은 깔끔한 맛 — 콜라겐 영양제임에도 비리지 않고 음료처럼 맛있어 먹기 편함</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr"/>
+          <t>비린내 없는 상큼한 맛 — 콜라겐 특유의 비린 맛 없이 상큼하고 맛있게 복용 가능</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>간편한 앰플형 제형 — 낱개 앰플 형태로 하루 하나씩 개봉해 마시기 수월함</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>다소 높은 가격대 부담 — 지속해서 가격이 인상되어 자가 섭취용으로 재구매하기에는 다소 주저하게 됨</t>
+          <t>부담스러운 가격 인상 — 가격대가 다소 높고 점차 가격이 올라 부담스러움</t>
         </is>
       </c>
       <c r="O12" t="inlineStr"/>
@@ -3241,22 +3281,22 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>퍽퍽함 없는 부드러운 맛 — 닭가슴살 본연의 맛을 유지하면서도 무척 촉촉하고 결이 연해 식감이 훌륭함</t>
+          <t>부드럽고 촉촉한 식감 — 닭가슴살임에도 퍽퍽하지 않고 매우 부드러움</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>다채로운 소스 옵션 — 다양한 형태와 여러 종류의 소스로 구성되어 지루하지 않게 체중 관리 가능함</t>
+          <t>질리지 않는 다양한 맛 — 다양한 종류의 소스와 맛으로 구성되어 식단 관리에 용이함</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>최상의 뛰어난 가성비 — 매우 저렴한 가격 대비 풍성한 팩 수량을 제공하여 가성비가 최고 수준임</t>
+          <t>가성비 뛰어난 구성 — 24개 닭가슴살을 3만 원 미만의 저렴한 가격에 구매 가능함</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>배송 도중 완전 해동 — 신선도 유지가 필요한 냉동 식품임에도 상자 내부의 닭가슴살이 완벽히 녹아 배송됨</t>
+          <t>배송 중 완전 해동 — 배송 과정에서 상품이 완전히 녹아서 도착함</t>
         </is>
       </c>
       <c r="O13" t="inlineStr"/>
@@ -3265,7 +3305,7 @@
     <row r="14" ht="38" customHeight="1">
       <c r="B14" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -3273,7 +3313,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>[그레인온] 골드 카무트 브랜드밀효소G 3개월분+10포증정(총100포) + 파로저당씬칩 증정</t>
+          <t>[그레인온] 골드 카무트 브랜드밀 효소 3개월(+선물포장) +파인키위효소+고단백질바 증정</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -3283,48 +3323,48 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>24,900원</t>
+          <t>46,900원</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/13180362</t>
+          <t>https://gift.kakao.com/product/13180343</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260911094744_fdcb15f83b684390b6fd43416e90d400.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260923111828_e9badd52c1a54899b5226c1eae768639.jpg</t>
         </is>
       </c>
       <c r="I14" t="n">
         <v>4</v>
       </c>
       <c r="J14" t="n">
-        <v>892</v>
+        <v>1679</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>체감되는 속의 편안함 — 기름진 식사 후 한 포 섭취 시 가스 참이 줄고 속이 무척 편안해짐</t>
+          <t>편안한 속과 소화 촉진 — 식후 섭취 시 속이 더부룩하지 않고 소화 및 배변 활동에 도움됨</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>놀랄 만한 기분 좋은 맛 — 고소하고 달달한 미숫가루 같은 풍미로 맛있게 먹을 수 있음</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>구버전과의 질감 차이 — 기존에 지속적으로 먹던 다른 카무트 효소와 질감이나 느낌이 달라 이질감이 듦</t>
-        </is>
-      </c>
+          <t>고소한 고구마맛 풍미 — 고구마 맛으로 거부감 없이 고소하고 맛있게 복용 가능</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>풍성한 사은품 증정 — 파로효소와 단백질바 등 다양한 사은품이 동봉되어 혜택이 좋음</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr"/>
     </row>
     <row r="15" ht="38" customHeight="1">
       <c r="B15" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -3332,62 +3372,62 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>[한끼통살] 닭가슴살 한달 식단 패키지 30팩+(증정)보냉백</t>
+          <t>[그레인온] 골드 카무트 브랜드밀효소G 3개월분+10포증정(총100포) + 파로저당씬칩 증정</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>한끼통살</t>
+          <t>그레인온</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>86,800원</t>
+          <t>24,900원</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/11566779</t>
+          <t>https://gift.kakao.com/product/13180362</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260429112212_3e1db89ad7174b6989286381ae7257c6.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260911094744_fdcb15f83b684390b6fd43416e90d400.jpg</t>
         </is>
       </c>
       <c r="I15" t="n">
         <v>4</v>
       </c>
       <c r="J15" t="n">
-        <v>151</v>
+        <v>892</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>포만감 가득한 식사 대용 — 한 팩만 꼭꼭 씹어 먹어도 위장이 가득 차 배고픔이 느껴지지 않음</t>
+          <t>속 편한 소화 개선 — 매일 한 포 섭취 시 속이 더부룩하지 않고 편안함</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>골라 먹는 골고루 식단 — 패키지 내에 여러 종류가 가득해 매일 다른 맛을 취향껏 골라 섭취 가능함</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr"/>
+          <t>착한 가격과 증정 구성 — 10포 추가 증정과 사은품 구성으로 가성비가 뛰어남</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>고소하고 맛있는 맛 — 효소 맛이 부담 없이 맛있어 꾸준히 먹기 좋음</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>패키지 오배송 및 누락 — 일부 품목이 제대로 조율되지 않고 겹치거나 다른 팩이 잘못 끼워져 배송됨</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>개별 팩 진공 불량 파손 — 비닐 팩 포장이 완전히 헐렁하여 소스가 외부 상자로 누출되거나 터짐</t>
-        </is>
-      </c>
+          <t>기존 제품과 다른 풍미 — 기존에 먹던 제품과 맛이 달라 다소 낯설음</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr"/>
     </row>
     <row r="16" ht="38" customHeight="1">
       <c r="B16" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -3395,48 +3435,60 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>[그레인온] 골드 카무트 브랜드밀 효소 3개월(+선물포장)</t>
+          <t>[한끼통살] 닭가슴살 한달 식단 패키지 30팩+(증정)보냉백</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>그레인온</t>
+          <t>한끼통살</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>46,900원</t>
+          <t>86,800원</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/13180343</t>
+          <t>https://gift.kakao.com/product/11566779</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260921093919_9881af9e82944da586785c0fe2e5715a.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260429112212_3e1db89ad7174b6989286381ae7257c6.jpg</t>
         </is>
       </c>
       <c r="I16" t="n">
         <v>4</v>
       </c>
       <c r="J16" t="n">
-        <v>1679</v>
+        <v>151</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>만족스러운 소화력 증진 — 식사 후 더부룩한 배를 편히 소화시켜 주고 원활한 배변 활동을 도우며 속을 케어함</t>
+          <t>뛰어난 맛과 높은 포만감 — 소스가 맛있고 한 팩만으로도 든든한 포만감을 제공함</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>친숙하고 맛난 구수함 — 달콤한 군고구마를 먹는 듯 고소하며 거부감 없이 쉽게 넘어감</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
+          <t>실용적인 보냉백 증정 — 사은품으로 증정된 도시락 가방이 예쁘고 들고 다니기 유용함</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>한 달 식단 대용량 — 30팩 대용량으로 구성되어 한 달 식단 관리에 적합함</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>구성 누락 및 오배송 — 정해진 구성품이 누락되고 중복 발송되었으나 문의 응답이 없음</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>포장 불량 및 소스 누출 — 진공 포장이 헐렁하거나 팩이 터져 소스가 묻어남</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr"/>
     </row>
     <row r="17" ht="38" customHeight="1">
@@ -3481,18 +3533,22 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>더부룩함 해결 효과 — 밀가루 등 기름진 식사 후에 먹었을 때 더부룩한 체증이 신속히 내려감</t>
+          <t>고소한 말차맛 효소 — 효소 특유의 냄새 없이 고소하고 맛있게 섭취 가능</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>매력적인 콜라보 특전 — 최애 아티스트 포토카드와 함께 단백질 바까지 알차게 챙길 수 있어 만족스러움</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr"/>
+          <t>더부룩함 없는 소화 개선 — 식후 복용 시 더부룩한 속이 편안해짐</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>굿즈 및 단백질바 구성 — 포토카드 증정과 단백질바 동봉 구성으로 가성비 만족도가 높음</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>발송 및 배송 지연 현상 — 기다리는 일정보다 배송이 늦게 출발하여 지연 수령함</t>
+          <t>다소 늦은 배송 속도 — 배송이 다소 늦은 편이라 수령까지 기다림이 있음</t>
         </is>
       </c>
       <c r="O17" t="inlineStr"/>
@@ -3540,17 +3596,17 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>비린 맛 제로 초코 풍미 — 단백질 음료 고유의 비리고 텁텁한 맛이 전혀 없으며 카페 초코우유처럼 달콤함</t>
+          <t>비린내 없는 깔끔한 맛 — 단백질 음료 특유의 비리고 텁텁한 맛 없이 달콤함</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>포만감 가득한 가벼운 대용 — 운동 후 피로를 풀고 출출한 상태를 부드럽게 완화할 정도의 충만한 포만감을 제공함</t>
+          <t>속 편한 포만감 유지 — 마신 뒤 속이 더부룩하지 않고 허기를 채우기에 적당함</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>속 쓰림 없는 원활한 소화 — 분리유청 단백질을 사용하여 마신 뒤에도 배가 부글거리지 않고 편안함</t>
+          <t>슬림한 팩의 휴대성 — 패키지가 슬림하여 가방에 넣어 운동 후 꺼내 마시기 편함</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -3599,25 +3655,25 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>화사하고 고급진 용기 — 공주풍의 세련된 틴케이스와 정교한 유리병 마감으로 소장용으로 뛰어남</t>
+          <t>예쁜 공주풍 용기 디자인 — 패키지와 앰플 병이 고급스럽고 예뻐 선물용으로 만족스러움</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>달달한 비타민 풍미 — 액상 비타민 특유의 활력 있고 시원한 맛으로 간식처럼 먹기 좋음</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr"/>
+          <t>상큼하고 맛있는 맛 — 비타500 같은 상큼한 맛으로 거부감 없이 맛있게 섭취함</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>간편한 액상 앰플형 — 정제 섭취가 부담스러운 사용자도 마시기 간편함</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>자극적인 감기약 맛 — 일부 입맛에 따라 다소 진하고 자극적인 시럽 약 느낌이 날 수 있음</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>단기 복용 시 미비한 변화 — 복용 기간이 다소 짧아 가시적인 피부 결이나 탄력 개선을 보기 어려움</t>
-        </is>
-      </c>
+          <t>단독 복용 시 진한 농도 — 액상이 다소 진하여 마신 후 물을 함께 마시게 됨</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr"/>
     </row>
     <row r="20" ht="38" customHeight="1">
@@ -3662,27 +3718,27 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>신속한 체력 충전 퍼포먼스 — 운동 전에 먹으면 지구력과 집중력이 향상되며 지치지 않게 컨디션을 살려줌</t>
+          <t>초고함량 아르기닌 배합 — 1포당 6,200mg 고함량으로 운동 시 지구력과 활력 향상에 도움됨</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>극대화된 초고함량 구성 — 1포에 6,200mg이라는 타 제품 대비 월등히 우수한 함량을 보유함</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>알약 타입의 커다란 크기 — 구성 성분 중 정제 제형의 알약이 다소 목에 걸릴 만큼 굵고 큼</t>
-        </is>
-      </c>
+          <t>간편한 1포 섭취 스틱 — 스틱 개별 포장이라 휴대성이 좋고 하루 한 포로 간편함</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>선물하기 좋은 패키징 — 쇼핑백과 추가 5포 증정으로 선물용 구성이 훌륭함</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr"/>
     </row>
     <row r="21" ht="38" customHeight="1">
       <c r="B21" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -3690,12 +3746,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>아메리카노 증정 에너지 활력선물 [김종국 추천세트]익스트림 아르기닌정 (2개월분) &amp; 밀크씨슬 플러스 (2개월분) + 쇼핑백 증정</t>
+          <t>BEST 프로틴모음 [랩노쉬] 프로틴 락커 12종 선물세트 (프로틴 드링크 퍼펙트, 단백쿠키, 단백 쿠키바)</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>익스트림</t>
+          <t>랩노쉬</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -3705,31 +3761,35 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/7556791</t>
+          <t>https://gift.kakao.com/product/12052312</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260904160657_c66395adeecf4b11a3a2afd7f4e2d479.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260723171929_09161ef5007a47039ea2ea7988556deb.jpg</t>
         </is>
       </c>
       <c r="I21" t="n">
         <v>4</v>
       </c>
       <c r="J21" t="n">
-        <v>1534</v>
+        <v>15</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>상쾌해진 기상 컨디션 — 아침에 일어날 때 몸이 무겁지 않고 가볍게 개어나는 효과를 경험함</t>
+          <t>다채로운 베스트 12종 — 드링크, 쿠키 등 다양한 제품을 한 번에 맛볼 수 있는 체험형 세트임</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>아르기닌과 밀크씨슬 구성 — 간 건강과 피로 회복을 두루 관리 가능한 올인원 복합 영양제 구성이라 간편함</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr"/>
+          <t>일반 간식 같은 단백질 — 프로틴 특유의 맛 없이 달콤하고 맛있게 단백질 섭취 가능함</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>선물 및 경품용 패키지 — 패키지가 크고 깔끔하여 운동 모임 경품이나 선물용으로 인기 있음</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr"/>
@@ -4052,16 +4112,16 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>16117</v>
+        <v>16119</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>15448</v>
+        <v>15450</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>3361</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="G7" s="3" t="n">
         <v>767</v>
@@ -4082,7 +4142,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="8" ht="60" customHeight="1">
+    <row r="8" ht="90" customHeight="1">
       <c r="B8" s="1" t="inlineStr">
         <is>
           <t>긍정리뷰</t>
@@ -4090,62 +4150,72 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>훌륭한 선물용 패키지 — 포장 상태가 깔끔하고 품격 있어 선물용으로 주고받기 좋음
-우수한 피로 회복 효과 — 섭취 후 체력이 회복되고 몸의 변화가 뚜렷하게 체감됨</t>
+          <t>피로 회복 및 활력 충전 — 섭취 후 피로가 풀리고 컨디션 회복에 도움됨
+선물용 높은 만족도 — 고급 비타민 이미지로 가볍게 선물하거나 받기에 좋음
+정돈된 꼼꼼한 포장 — 배송 시 제품 포장이 깔끔하게 정돈되어 도착함</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>편리한 휴대와 섭취 — 액상 제형으로 한 포씩 챙겨 먹기 편해 일상에서 손이 자주 감
-기분 좋은 활력 충전 — 복용 후 피로가 풀리고 활력이 생기는 데 도움을 줌</t>
+          <t>편리한 액상형 섭취 — 액상 제형이라 챙겨 먹기 편하고 손이 자주 감
+선물용 고급 패키지 — 포장이 고급스러워 생일이나 응원 선물로 받기 좋음
+피로 개선 및 기력 회복 — 복용 후 활력이 생기고 피로 회복에 도움됨</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>확실한 컨디션 회복 — 섭취 후 기력이 약해진 상태나 피로감이 눈에 띄게 완화됨
-고급스러운 케이스 포장 — 명절 분위기에 어울리는 화사하고 예쁜 케이스에 담겨서 옴</t>
+          <t>뛰어난 피로 회복 효과 — 섭취 후 피로감이 줄고 일상 활력 증진에 도움됨
+고급스러운 명절 선물 — 패키지가 예쁘고 고급스러워 추석이나 생일 선물용으로 적합함
+합리적인 가격 구성 — 대용량 구성 대비 좋은 가격대로 구매 가능함</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>실용적인 포장 방식 — 개별 포장되어 있어 가방이나 사무실 책상에 보관하며 챙기기 용이함
-빠른 에너지 보충 — 힘든 일정 시작 전 복용 시 기력 충전에 실질적인 도움을 줌</t>
+          <t>즉각적인 활력 충전 — 섭취 시 힘이 나고 피로 회복에 빠른 체감 효과 있음
+간편한 개별 포장 휴대 — 한 포씩 개별 포장되어 가방이나 책상에 두고 챙기기 용이함
+선물용 고급스러운 외관 — 포장 상태가 좋고 고급스러워 지인 선물로 만족스러움</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>뛰어난 활력 증진 효과 — 섭취 당일의 활력과 전반적인 신체 컨디션 증진에 탁월함
-선물하기 최적화된 포장 — 추가 종이 쇼핑백이 동봉되어 정성 가득한 선물용으로 아주 적합함</t>
+          <t>피로 회복 및 컨디션 향상 — 복용 후 피로가 풀리고 하루 활력 유지에 뛰어남
+휴대 및 섭취 편의성 — 여행이나 일상에서 한 병씩 들고 다니며 챙겨 먹기 편함
+쇼핑백 동봉 깔끔한 포장 — 종이봉투가 동봉되어 깔끔하게 선물하거나 전달하기 좋음</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>체감되는 기력 충전 — 저녁 섭취 시 활력이 넘쳐 수면을 이루기 힘들 정도로 에너지 충전 효과가 강함
-풍성한 서비스 증정 — 본품 외에 추가 증정품 혜택이 있어 기분 좋게 섭취할 수 있음</t>
+          <t>즉각적인 활력 및 기운 — 섭취 후 급한 피로가 풀리고 눈에 띄게 힘이 남
+푸짐한 추가 증정 혜택 — 서비스 추가 증정 구성이 포함되어 만족도가 높음
+선물에 적합한 예쁜 포장 — 포장이 꼼꼼하고 예뻐 생일이나 위시리스트 선물용으로 적합함</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>부담 없는 젤리 제형 — 물 없이 가볍게 씹어서 삼키는 구미 타입이라 섭취 과정이 매우 간편함
-거부감 없는 달콤한 맛 — 특유의 비린 향이 전혀 없고 익숙한 과일 맛 젤리 같아 꾸준히 챙기기 좋음</t>
+          <t>맛있는 젤리 제형 — 마이구미처럼 달콤하고 맛있어 거부감 없이 섭취 가능
+물 없는 간편한 섭취 — 물이 필요 없어 출근 전이나 일상에서 간편하게 복용함
+귀엽고 깔끔한 패키지 — 포장이 깔끔하고 키캡 증정 등 가볍게 선물하기 적합함</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>간편한 복용 타입 — 액상과 분말이 결합한 형태로 별도의 물 없이 편리하게 즉각 복용 가능함
-신뢰할 수 있는 브랜드 — 정관장 브랜드 명성에 걸맞은 세련된 포장과 입증된 효능으로 높은 만족감을 줌</t>
+          <t>정관장 브랜드 신뢰도 — 정관장 브랜드 제품이라 성분과 품질을 믿고 섭취함
+올인원 간편 섭취 — 액상과 분말이 함께 있어 물 없이 하루 한 병 섭취 용이함
+뚜렷한 에너지 보충 효과 — 피곤할 때 마시면 밤잠을 설칠 정도로 기력 보충에 도움됨</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>피로 감소 및 면역 관리 — 꾸준히 복용할 시 피로감이 줄고 컨디션 유지 및 관리에 상당한 보탬이 됨
-맞춤형 맞춤 설계 구성 — 성별 맞춤형 바이탈 옵션을 별도로 지정해 먹을 수 있어 실용적임</t>
+          <t>성별 맞춤 영양 설계 — 성별에 맞춰 m/f 선택이 가능하고 풍부한 영양소 함유
+지속적인 피로 개선 — 꾸준히 복용 시 피로감이 줄고 반짝이는 기운이 유지됨
+정성 가득한 패키지 — 포장이 깔끔하여 성의 있는 선물로 제격임</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>간편한 아침 건강 챙김 — 액상과 정제를 한 번에 섭취 가능한 편리한 디자인으로 아침 대용으로 훌륭함
-매우 정성스러운 패키지 — 선물 상자 자체에 신경을 많이 쓴 티가 날 정도로 튼튼하고 고급스러움</t>
+          <t>빠른 피로 회복 체감 — 섭취 시 피로 회복이 빠르고 컨디션 유지에 좋음
+간편한 복합 제형 섭취 — 액상과 정제를 한 번에 섭취할 수 있어 바쁜 일상에 간편함
+넉넉한 30일분 구성 — 합리적인 가격에 30일분 대용량이라 장기 관리에 유용함</t>
         </is>
       </c>
     </row>
@@ -4157,41 +4227,37 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>포장 구성품 누락 — 선물용 에디션임에도 쇼핑백이 동봉되지 않아 개별 구매가 필요함
-배송 중 박스 훼손 — 배송 도중 상자가 군데군데 찌그러진 상태로 수령됨</t>
+          <t>쇼핑백 별도 구매 불편 — 기프트 에디션임에도 쇼핑백이 동봉되지 않아 따로 구매해야 함
+박스 파손 및 적은 용량 — 외관 상자가 찌그러져 오거나 8일분 용량이 맛보기 수준으로 아쉬움</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>다소 늦어진 배송 — 배송 완료까지 다소 많은 시일이 소요되어 아쉬움</t>
+          <t>다소 느린 배송 속도 — 주문 후 배송이 늦게 도착함</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>동봉된 쇼핑백 불량 — 함께 제공된 선물용 가방이 파손된 채 배송되어 온전한 사용이 불가능함</t>
+          <t>쇼핑백 불량 및 파손 — 동봉된 쇼핑백 상태가 불량하여 선물용 전달에 불편함 발생</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>배송 요청사항 미반영 — 부재 시 관리실 위탁을 요청하였으나 문 앞에 두고 가 아쉬움이 남음</t>
+          <t>배송 요청사항 미반영 — 부재 시 관리실 위탁 요청이 반영되지 않고 문 앞에 두고 감</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr"/>
       <c r="H9" s="3" t="inlineStr"/>
       <c r="I9" s="3" t="inlineStr"/>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t>늦은 시간 섭취 시 각성 — 늦은 저녁에 복용할 경우 강한 각성 작용으로 인해 밤을 새울 우려가 있음</t>
-        </is>
-      </c>
+      <c r="J9" s="3" t="inlineStr"/>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>다소 부담스러운 제제 — 기존 제품들에 비해 알약의 물리적 크기가 커 목넘김에 다소 어려움이 있음</t>
+          <t>부담스러운 정제 크기 — 기존 제품 대비 알약 크기가 커서 삼키기 다소 힘듦</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>밀봉 씰 및 패키지 오염 — 밀봉 테이프가 여러 번 뗐다 붙인 듯 훼손되어 있고 상자 표면에 손자국과 먼지가 묻어 있음</t>
+          <t>봉인 씰 훼손 및 오염 — 밀봉 스티커가 떼어졌다 붙은 흔적과 손자국 등 이물질이 묻어 있음</t>
         </is>
       </c>
     </row>
@@ -4401,42 +4467,42 @@
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
           <t>기타/특수목적</t>
         </is>
       </c>
-      <c r="F15" s="3" t="inlineStr">
+      <c r="G15" s="3" t="inlineStr">
         <is>
           <t>다이어트/체중관리</t>
         </is>
       </c>
-      <c r="G15" s="3" t="inlineStr">
+      <c r="H15" s="3" t="inlineStr">
         <is>
           <t>기타/특수목적</t>
         </is>
       </c>
-      <c r="H15" s="3" t="inlineStr">
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>피부/미용</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+      <c r="L15" s="3" t="inlineStr">
         <is>
           <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="I15" s="3" t="inlineStr">
-        <is>
-          <t>다이어트/체중관리</t>
-        </is>
-      </c>
-      <c r="J15" s="3" t="inlineStr">
-        <is>
-          <t>피부/미용</t>
-        </is>
-      </c>
-      <c r="K15" s="3" t="inlineStr">
-        <is>
-          <t>다이어트/체중관리</t>
-        </is>
-      </c>
-      <c r="L15" s="3" t="inlineStr">
-        <is>
-          <t>다이어트/체중관리</t>
         </is>
       </c>
     </row>
@@ -4463,19 +4529,19 @@
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
+          <t>그레인온</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr">
+        <is>
           <t>한끼통살</t>
         </is>
       </c>
-      <c r="G16" s="3" t="inlineStr">
+      <c r="H16" s="3" t="inlineStr">
         <is>
           <t>그레인온</t>
         </is>
       </c>
-      <c r="H16" s="3" t="inlineStr">
-        <is>
-          <t>그레인온</t>
-        </is>
-      </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
           <t>셀렉스</t>
@@ -4493,7 +4559,7 @@
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>익스트림</t>
+          <t>랩노쉬</t>
         </is>
       </c>
     </row>
@@ -4515,19 +4581,19 @@
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
+          <t>[그레인온] 골드 카무트 브랜드밀 효소 3개월(+선물포장) +파인키위효소+고단백질바 증정</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
           <t>[그레인온] 골드 카무트 브랜드밀효소G 3개월분+10포증정(총100포) + 파로저당씬칩 증정</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
+      <c r="G17" s="3" t="inlineStr">
         <is>
           <t>[한끼통살] 닭가슴살 한달 식단 패키지 30팩+(증정)보냉백</t>
         </is>
       </c>
-      <c r="G17" s="3" t="inlineStr">
-        <is>
-          <t>[그레인온] 골드 카무트 브랜드밀 효소 3개월(+선물포장)</t>
-        </is>
-      </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
           <t>[리센느에디션] 베리말차 캡슐레이션 효소 1.8g 30포, 2개</t>
@@ -4550,7 +4616,7 @@
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t>아메리카노 증정 에너지 활력선물 [김종국 추천세트]익스트림 아르기닌정 (2개월분) &amp; 밀크씨슬 플러스 (2개월분) + 쇼핑백 증정</t>
+          <t>BEST 프로틴모음 [랩노쉬] 프로틴 락커 12종 선물세트 (프로틴 드링크 퍼펙트, 단백쿠키, 단백 쿠키바)</t>
         </is>
       </c>
     </row>
@@ -4604,13 +4670,13 @@
         <v>54</v>
       </c>
       <c r="E19" s="3" t="n">
+        <v>1679</v>
+      </c>
+      <c r="F19" s="3" t="n">
         <v>892</v>
       </c>
-      <c r="F19" s="3" t="n">
+      <c r="G19" s="3" t="n">
         <v>151</v>
-      </c>
-      <c r="G19" s="3" t="n">
-        <v>1679</v>
       </c>
       <c r="H19" s="3" t="n">
         <v>99</v>
@@ -4625,7 +4691,7 @@
         <v>248</v>
       </c>
       <c r="L19" s="3" t="n">
-        <v>1534</v>
+        <v>15</v>
       </c>
     </row>
     <row r="20" ht="90" customHeight="1">
@@ -4636,64 +4702,72 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>우아한 보자기 선물 포장 — 보자기와 틴케이스를 결합한 화려한 비주얼로 개봉 시 깊은 만족을 선사함
-비리지 않은 깔끔한 맛 — 콜라겐 영양제임에도 비리지 않고 음료처럼 맛있어 먹기 편함</t>
+          <t>고급스러운 보자기 포장 — 틴케이스와 보자기, 쇼핑백 등 선물 포장이 매우 정성스러움
+비린내 없는 상큼한 맛 — 콜라겐 특유의 비린 맛 없이 상큼하고 맛있게 복용 가능
+간편한 앰플형 제형 — 낱개 앰플 형태로 하루 하나씩 개봉해 마시기 수월함</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>퍽퍽함 없는 부드러운 맛 — 닭가슴살 본연의 맛을 유지하면서도 무척 촉촉하고 결이 연해 식감이 훌륭함
-다채로운 소스 옵션 — 다양한 형태와 여러 종류의 소스로 구성되어 지루하지 않게 체중 관리 가능함
-최상의 뛰어난 가성비 — 매우 저렴한 가격 대비 풍성한 팩 수량을 제공하여 가성비가 최고 수준임</t>
+          <t>부드럽고 촉촉한 식감 — 닭가슴살임에도 퍽퍽하지 않고 매우 부드러움
+질리지 않는 다양한 맛 — 다양한 종류의 소스와 맛으로 구성되어 식단 관리에 용이함
+가성비 뛰어난 구성 — 24개 닭가슴살을 3만 원 미만의 저렴한 가격에 구매 가능함</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>체감되는 속의 편안함 — 기름진 식사 후 한 포 섭취 시 가스 참이 줄고 속이 무척 편안해짐
-놀랄 만한 기분 좋은 맛 — 고소하고 달달한 미숫가루 같은 풍미로 맛있게 먹을 수 있음</t>
+          <t>편안한 속과 소화 촉진 — 식후 섭취 시 속이 더부룩하지 않고 소화 및 배변 활동에 도움됨
+고소한 고구마맛 풍미 — 고구마 맛으로 거부감 없이 고소하고 맛있게 복용 가능
+풍성한 사은품 증정 — 파로효소와 단백질바 등 다양한 사은품이 동봉되어 혜택이 좋음</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>포만감 가득한 식사 대용 — 한 팩만 꼭꼭 씹어 먹어도 위장이 가득 차 배고픔이 느껴지지 않음
-골라 먹는 골고루 식단 — 패키지 내에 여러 종류가 가득해 매일 다른 맛을 취향껏 골라 섭취 가능함</t>
+          <t>속 편한 소화 개선 — 매일 한 포 섭취 시 속이 더부룩하지 않고 편안함
+착한 가격과 증정 구성 — 10포 추가 증정과 사은품 구성으로 가성비가 뛰어남
+고소하고 맛있는 맛 — 효소 맛이 부담 없이 맛있어 꾸준히 먹기 좋음</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>만족스러운 소화력 증진 — 식사 후 더부룩한 배를 편히 소화시켜 주고 원활한 배변 활동을 도우며 속을 케어함
-친숙하고 맛난 구수함 — 달콤한 군고구마를 먹는 듯 고소하며 거부감 없이 쉽게 넘어감</t>
+          <t>뛰어난 맛과 높은 포만감 — 소스가 맛있고 한 팩만으로도 든든한 포만감을 제공함
+실용적인 보냉백 증정 — 사은품으로 증정된 도시락 가방이 예쁘고 들고 다니기 유용함
+한 달 식단 대용량 — 30팩 대용량으로 구성되어 한 달 식단 관리에 적합함</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>더부룩함 해결 효과 — 밀가루 등 기름진 식사 후에 먹었을 때 더부룩한 체증이 신속히 내려감
-매력적인 콜라보 특전 — 최애 아티스트 포토카드와 함께 단백질 바까지 알차게 챙길 수 있어 만족스러움</t>
+          <t>고소한 말차맛 효소 — 효소 특유의 냄새 없이 고소하고 맛있게 섭취 가능
+더부룩함 없는 소화 개선 — 식후 복용 시 더부룩한 속이 편안해짐
+굿즈 및 단백질바 구성 — 포토카드 증정과 단백질바 동봉 구성으로 가성비 만족도가 높음</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>비린 맛 제로 초코 풍미 — 단백질 음료 고유의 비리고 텁텁한 맛이 전혀 없으며 카페 초코우유처럼 달콤함
-포만감 가득한 가벼운 대용 — 운동 후 피로를 풀고 출출한 상태를 부드럽게 완화할 정도의 충만한 포만감을 제공함
-속 쓰림 없는 원활한 소화 — 분리유청 단백질을 사용하여 마신 뒤에도 배가 부글거리지 않고 편안함</t>
+          <t>비린내 없는 깔끔한 맛 — 단백질 음료 특유의 비리고 텁텁한 맛 없이 달콤함
+속 편한 포만감 유지 — 마신 뒤 속이 더부룩하지 않고 허기를 채우기에 적당함
+슬림한 팩의 휴대성 — 패키지가 슬림하여 가방에 넣어 운동 후 꺼내 마시기 편함</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>화사하고 고급진 용기 — 공주풍의 세련된 틴케이스와 정교한 유리병 마감으로 소장용으로 뛰어남
-달달한 비타민 풍미 — 액상 비타민 특유의 활력 있고 시원한 맛으로 간식처럼 먹기 좋음</t>
+          <t>예쁜 공주풍 용기 디자인 — 패키지와 앰플 병이 고급스럽고 예뻐 선물용으로 만족스러움
+상큼하고 맛있는 맛 — 비타500 같은 상큼한 맛으로 거부감 없이 맛있게 섭취함
+간편한 액상 앰플형 — 정제 섭취가 부담스러운 사용자도 마시기 간편함</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>신속한 체력 충전 퍼포먼스 — 운동 전에 먹으면 지구력과 집중력이 향상되며 지치지 않게 컨디션을 살려줌
-극대화된 초고함량 구성 — 1포에 6,200mg이라는 타 제품 대비 월등히 우수한 함량을 보유함</t>
+          <t>초고함량 아르기닌 배합 — 1포당 6,200mg 고함량으로 운동 시 지구력과 활력 향상에 도움됨
+간편한 1포 섭취 스틱 — 스틱 개별 포장이라 휴대성이 좋고 하루 한 포로 간편함
+선물하기 좋은 패키징 — 쇼핑백과 추가 5포 증정으로 선물용 구성이 훌륭함</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>상쾌해진 기상 컨디션 — 아침에 일어날 때 몸이 무겁지 않고 가볍게 개어나는 효과를 경험함
-아르기닌과 밀크씨슬 구성 — 간 건강과 피로 회복을 두루 관리 가능한 올인원 복합 영양제 구성이라 간편함</t>
+          <t>다채로운 베스트 12종 — 드링크, 쿠키 등 다양한 제품을 한 번에 맛볼 수 있는 체험형 세트임
+일반 간식 같은 단백질 — 프로틴 특유의 맛 없이 달콤하고 맛있게 단백질 섭취 가능함
+선물 및 경품용 패키지 — 패키지가 크고 깔끔하여 운동 모임 경품이나 선물용으로 인기 있음</t>
         </is>
       </c>
     </row>
@@ -4705,43 +4779,38 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>다소 높은 가격대 부담 — 지속해서 가격이 인상되어 자가 섭취용으로 재구매하기에는 다소 주저하게 됨</t>
+          <t>부담스러운 가격 인상 — 가격대가 다소 높고 점차 가격이 올라 부담스러움</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>배송 도중 완전 해동 — 신선도 유지가 필요한 냉동 식품임에도 상자 내부의 닭가슴살이 완벽히 녹아 배송됨</t>
-        </is>
-      </c>
-      <c r="E21" s="3" t="inlineStr">
-        <is>
-          <t>구버전과의 질감 차이 — 기존에 지속적으로 먹던 다른 카무트 효소와 질감이나 느낌이 달라 이질감이 듦</t>
-        </is>
-      </c>
+          <t>배송 중 완전 해동 — 배송 과정에서 상품이 완전히 녹아서 도착함</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr"/>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>패키지 오배송 및 누락 — 일부 품목이 제대로 조율되지 않고 겹치거나 다른 팩이 잘못 끼워져 배송됨
-개별 팩 진공 불량 파손 — 비닐 팩 포장이 완전히 헐렁하여 소스가 외부 상자로 누출되거나 터짐</t>
-        </is>
-      </c>
-      <c r="G21" s="3" t="inlineStr"/>
+          <t>기존 제품과 다른 풍미 — 기존에 먹던 제품과 맛이 달라 다소 낯설음</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>구성 누락 및 오배송 — 정해진 구성품이 누락되고 중복 발송되었으나 문의 응답이 없음
+포장 불량 및 소스 누출 — 진공 포장이 헐렁하거나 팩이 터져 소스가 묻어남</t>
+        </is>
+      </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>발송 및 배송 지연 현상 — 기다리는 일정보다 배송이 늦게 출발하여 지연 수령함</t>
+          <t>다소 늦은 배송 속도 — 배송이 다소 늦은 편이라 수령까지 기다림이 있음</t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr"/>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>자극적인 감기약 맛 — 일부 입맛에 따라 다소 진하고 자극적인 시럽 약 느낌이 날 수 있음
-단기 복용 시 미비한 변화 — 복용 기간이 다소 짧아 가시적인 피부 결이나 탄력 개선을 보기 어려움</t>
-        </is>
-      </c>
-      <c r="K21" s="3" t="inlineStr">
-        <is>
-          <t>알약 타입의 커다란 크기 — 구성 성분 중 정제 제형의 알약이 다소 목에 걸릴 만큼 굵고 큼</t>
-        </is>
-      </c>
+          <t>단독 복용 시 진한 농도 — 액상이 다소 진하여 마신 후 물을 함께 마시게 됨</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="inlineStr"/>
       <c r="L21" s="3" t="inlineStr"/>
     </row>
     <row r="22">
@@ -4762,17 +4831,17 @@
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
+          <t>46,900원</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
           <t>24,900원</t>
         </is>
       </c>
-      <c r="F22" s="3" t="inlineStr">
+      <c r="G22" s="3" t="inlineStr">
         <is>
           <t>86,800원</t>
-        </is>
-      </c>
-      <c r="G22" s="3" t="inlineStr">
-        <is>
-          <t>46,900원</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
@@ -4987,7 +5056,7 @@
     <row r="2" ht="38" customHeight="1">
       <c r="B2" t="inlineStr">
         <is>
-          <t>루테인/눈건강</t>
+          <t>혈행</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -4995,7 +5064,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>대웅제약 rTG오메가3 6캡슐 6일분</t>
+          <t>대웅제약 코엔자임Q10 6캡슐 6일분</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -5010,28 +5079,28 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000269&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000279&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260504/LdyaPluhRl2HSeYjB2pX600000269_00_01LdyaPluhRl2HSeYjB2pX.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260504/OqWOmDxWU1qoZh2gUZfq600000279_00_01OqWOmDxWU1qoZh2gUZfq.png</t>
         </is>
       </c>
       <c r="I2" t="n">
         <v>4.8</v>
       </c>
       <c r="J2" t="n">
-        <v>507</v>
+        <v>333</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>놀라운 가성비 혜택 — 다이소의 장점을 극대화한 가격 경쟁력으로 부담 없이 구매해 복용함</t>
+          <t>부담 없는 소량 포장 — 6일분 소용량으로 필요할 때 부담 없이 구매 가능함</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>휴대성 만점 미니 포장 — 가볍게 6일 단위로 개별 포장되어 타지로 갈 때 주머니나 파우치에 넣기 좋음</t>
+          <t>깔끔하고 간편한 휴대 — 소포장으로 나뉘어 있어 가방에 넣고 다니며 챙겨 먹기 편함</t>
         </is>
       </c>
       <c r="M2" t="inlineStr"/>
@@ -5042,7 +5111,7 @@
     <row r="3" ht="38" customHeight="1">
       <c r="B3" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -5050,51 +5119,47 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>[신혜선 PICK] 동국 마이팝 푸룬＆식이섬유</t>
+          <t>대웅제약 바나바잎 추출물 30정 30일분</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2,000원</t>
+          <t>3,000원</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=610911029&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000131&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260623/QaObI3LjZ86tREQcCYCw610911029_00_00QaObI3LjZ86tREQcCYCw.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/rCiQaBH4VQ1rKKr7rz83600000131_00_00rCiQaBH4VQ1rKKr7rz83.png</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="J3" t="n">
-        <v>469</v>
+        <v>4757</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>초고속 직빵 장 비우기 — 마신 지 약 한 시간 만에 아랫배에 신호가 와 장을 말끔히 청소함</t>
+          <t>다이소다운 착한 가성비 — 저렴한 가격으로 한 달 분량 혈당 관리 정제를 구매함</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>배앓이 없는 안전한 작용 — 인위적으로 강한 배 통증을 자극하지 않고 부드럽게 쾌변할 수 있도록 도와줌</t>
+          <t>식전 간편한 1정 복용 — 식사 전 한 알로 간편하게 혈당 스파이크 관리에 도움을 기대함</t>
         </is>
       </c>
       <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>지나치게 잦은 설사 유도 — 개인 위장 상태에 따라 너무 강력하게 작용하여 설사가 동반될 우려가 있음</t>
-        </is>
-      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
     </row>
@@ -5109,7 +5174,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>닥터블릿 푸응 7days 팻버닝 21캡슐</t>
+          <t>닥터블릿 멜라드림 30정 30일분</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -5124,28 +5189,28 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=613602085&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=031930043&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260624/m6tznB24o1VYvw4vwVs3613602085_00_00m6tznB24o1VYvw4vwVs3.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260106/ifUNcDpBRic8ZZffJeay031930043_00_03ifUNcDpBRic8ZZffJeay.jpg</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="J4" t="n">
-        <v>2700</v>
+        <v>1708</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>체지방 축적 방지 보조 — 과식이나 기름진 음식을 다량 먹었을 때 살이 찌지 않게 체지방 관리를 보조함</t>
+          <t>빠른 입면과 숙면 유도 — 복용 후 20~30분 내로 졸음이 오며 중간에 깨지 않고 깊게 잠듦</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>상당한 대변 기능 향상 — 변비로 묵직했던 위장을 시원하게 비워주는 데 실질적 도움을 줌</t>
+          <t>뛰어난 가성비 수면템 — 비싼 수면 보조제 대비 저렴한 가격으로 수면의 질을 개선함</t>
         </is>
       </c>
       <c r="M4" t="inlineStr"/>
@@ -5156,7 +5221,7 @@
     <row r="5" ht="38" customHeight="1">
       <c r="B5" t="inlineStr">
         <is>
-          <t>비타민D</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -5164,7 +5229,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>동국제약 비타민D 2000IU 40캡슐 40일분</t>
+          <t>[산뜻한 상쾌함] [신혜선 PICK] 동국제약 프로폴리스 프레쉬볼 레몬＆민트 20캡슐 20일분</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -5179,39 +5244,47 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=610910777&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=610911102&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20251229/5qFLremik89lsUa72Yqy610910777_00_005qFLremik89lsUa72Yqy.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260907/D3MtLfS4wvzyyoiG4ppT610911102_00_01D3MtLfS4wvzyyoiG4ppT.jpg</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="J5" t="n">
-        <v>1131</v>
+        <v>75</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>매우 작은 초소형 캡슐 — 캡슐 크기가 획기적으로 작아 노약자도 부드럽고 수월하게 목으로 넘김</t>
+          <t>즉각적인 구강 상쾌함 — 작은 알을 터뜨리면 입안이 시원해지고 구취 관리에 도움됨</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>가루 대비 부드러운 섭취 — 시거나 자극적인 맛의 비타민 분말과 달리 신맛이 전혀 느껴지지 않아 간편함</t>
+          <t>가성비 좋은 데일리템 — 가격이 저렴하여 일상에서 부담 없이 구강 청결용으로 쓰기 좋음</t>
         </is>
       </c>
       <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>자극적인 민트 매운맛 — 민트 맛이 다소 강해 매운맛에 민감하면 자극적으로 느껴짐</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>부족한 캡슐 내용물 — 캡슐 안 액상 내용물 용량이 적어 한 번에 2알을 복용하게 됨</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr"/>
     </row>
     <row r="6" ht="38" customHeight="1">
       <c r="B6" t="inlineStr">
         <is>
-          <t>비타민C/항산화</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -5219,12 +5292,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>대웅제약 비타민C 30정 30일분</t>
+          <t>종근당건강 락토핏 골드</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>대웅제약</t>
+          <t>종근당건강</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -5234,28 +5307,28 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000127&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=591580521&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250408/V0qSVbLLgSaCWbYWEu73600000127_00_00V0qSVbLLgSaCWbYWEu73.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260522/0jgRGoNZEcwwrbTgrqVw591580521_00_000jgRGoNZEcwwrbTgrqVw.jpg</t>
         </is>
       </c>
       <c r="I6" t="n">
         <v>4.8</v>
       </c>
       <c r="J6" t="n">
-        <v>2682</v>
+        <v>1622</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>우수한 극가성비 비타민 — 하루 일정 함량 이상의 필요한 성분을 매달 저렴하고 쉽게 공급할 수 있음</t>
+          <t>복부 가스 및 팽만 완화 — 배에 가스가 차는 증상을 줄여주고 편안한 장 환경에 도움됨</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>느껴지는 피로 예방 효과 — 꾸준히 복용 시 아침 일과 진행 시 기력이 크게 처지는 것을 예방함</t>
+          <t>부담 없는 저렴한 가격 — 다이소몰에서 저렴하게 구매할 수 있어 재구매 의사 높음</t>
         </is>
       </c>
       <c r="M6" t="inlineStr"/>
@@ -5266,7 +5339,7 @@
     <row r="7" ht="38" customHeight="1">
       <c r="B7" t="inlineStr">
         <is>
-          <t>홍삼/인삼</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -5274,12 +5347,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>휴럼 하루한알 6년근 고려 홍삼환 9환 9일분</t>
+          <t>닥터블릿 푸응 7days 팻버닝 21캡슐</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>휴럼</t>
+          <t>닥터블릿</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -5289,43 +5362,39 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=919157095&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=613602085&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260826/gxSEg0bfLulOAScPenvi919157095_00_01gxSEg0bfLulOAScPenvi.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260624/m6tznB24o1VYvw4vwVs3613602085_00_00m6tznB24o1VYvw4vwVs3.jpg</t>
         </is>
       </c>
       <c r="I7" t="n">
         <v>4.7</v>
       </c>
       <c r="J7" t="n">
-        <v>66</v>
+        <v>2701</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>부드럽고 유연한 섭취 환 — 홍삼의 짙은 향이 지나치지 않아 입에서 가볍게 깨물어 간편히 복용할 수 있음</t>
+          <t>다이어트 체지방 관리 — 명절이나 단기 다이어트 시 체지방 관리 목적으로 섭취하기 좋음</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>순수 홍삼 위주의 안전 배합 — 체질에 안 맞을 수 있는 녹용이 빠지고 홍삼만 들어가 예민한 분도 안심하고 먹음</t>
+          <t>개별 포장의 휴대 편의 — 낱개 포장이라 휴대하기 간편하고 챙겨 먹기 수월함</t>
         </is>
       </c>
       <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>다소 미미한 홍삼의 잔향 — 전통적인 홍삼 특유의 깊은 한방 향이나 기운이 약하게 퍼지는 듯함</t>
-        </is>
-      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
     </row>
     <row r="8" ht="38" customHeight="1">
       <c r="B8" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -5333,54 +5402,62 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LG생활건강 이너뷰 다이어트 가르시니아 10포</t>
+          <t>[옥수수수염＆호박] 동국제약 맛있는 센텔라 공주캔디 20정 20일분</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>이너뷰 바이 리튠</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>3,000원</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=994953535&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=610911213&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250627/nv6m1SoKa2Zw57OA3JHL994953535_00_00nv6m1SoKa2Zw57OA3JHL.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260907/E3CpURjLLswf9MgzRChF610911213_00_01E3CpURjLLswf9MgzRChF.jpg</t>
         </is>
       </c>
       <c r="I8" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="J8" t="n">
-        <v>1012</v>
+        <v>64</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>식사 후 빠른 탄수 관리 — 식사 시 빵이나 면류를 대량 복용한 날 편리하게 물에 연하게 풀어 타 마시기 수월함</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr"/>
+          <t>새콤달콤한 복숭아맛 — 달콤하고 상큼한 맛으로 간식처럼 거부감 없이 복용함</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>붓기 관리 및 체감 효과 — 섭취 후 붓기 완화 효과를 비교적 빠르게 체감함</t>
+        </is>
+      </c>
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>입에 남는 잔여 약 맛 — 간식처럼 가볍게 타 먹기 좋은 제형이나 미미하게 인위적인 제제 향이 입안에 남음</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr"/>
+          <t>복숭아 알레르기 유발 — 복숭아 분말이 함유되어 복숭아 알레르기 유발 위험이 있음</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>버전별 맛 선호도 차이 — 기존 초록색 제품에 비해 복숭아 맛이 덜 맛있게 느껴짐</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr"/>
     </row>
     <row r="9" ht="38" customHeight="1">
       <c r="B9" t="inlineStr">
         <is>
-          <t>프로바이오틱스/유산균</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -5388,58 +5465,54 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>유한양행 초코맛 생유산균 스틱 20포 20일분</t>
+          <t>대웅제약 비타민B 30정 30일분</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>유한양행</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>3,000원</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600651652&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000129&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260325/dj7lmBMZiAKAXlm5drGt600651652_00_00dj7lmBMZiAKAXlm5drGt.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/5QghHD5oyZssCfnGZbzA600000129_00_005QghHD5oyZssCfnGZbzA.png</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="J9" t="n">
-        <v>448</v>
+        <v>2197</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>매력적인 진한 초콜릿향 — 기존 맛없는 영양제와 다르게 진한 카카오 맛이 퍼져 디저트 대용으로 훌륭함</t>
+          <t>온 가족 데일리 비타민 — 온 가족이 함께 매일 꾸준히 복용하기에 적합함</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>아이들이 좋아하는 대중성 — 부모가 보채지 않아도 편식하는 어린이가 먼저 스스로 찾아 섭취함</t>
+          <t>믿을 수 있는 제약사 — 대웅제약 브랜드 제품으로 신뢰하고 구매함</t>
         </is>
       </c>
       <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>일시적인 소화 이상 증세 — 체질이나 상태에 따라 가벼운 설사 증세 등 속이 다소 맞지 않는 경우가 있음</t>
-        </is>
-      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
     </row>
     <row r="10" ht="38" customHeight="1">
       <c r="B10" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -5447,58 +5520,58 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>[다영 PICK] 셀트리온 다이어트 한 잔 슬림 S 프레소 10포 5일분</t>
+          <t>홀베리 유기농 10포 레몬생강즙</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>셀트리온</t>
+          <t>홀베리</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2,000원</t>
+          <t>5,000원</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=944863413&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=965923424&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260605/8ADhx4mYwiTujsVcCSTD944863413_00_018ADhx4mYwiTujsVcCSTD.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260904/TyBV46Gp3x0VYWqJvrvs965923424_00_00TyBV46Gp3x0VYWqJvrvs.jpg</t>
         </is>
       </c>
       <c r="I10" t="n">
         <v>4.7</v>
       </c>
       <c r="J10" t="n">
-        <v>2606</v>
+        <v>533</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>깔끔한 아메리카노 맛 대용 — 피로를 깨울 겸 에스프레소 느낌의 카페인 음료처럼 부담 없이 타 마시기 적절함</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr"/>
+          <t>부담 없는 저렴한 가격 — 인터넷 판매가 대비 저렴한 가격으로 구매 만족도 높음</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>무가당 건강 레몬생강 — 당분이 없어 따뜻한 물과 꿀에 타 먹기 좋음</t>
+        </is>
+      </c>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
-          <t>다소 극단적으로 쓴 풍미 — 약재가 결합하여 평소 먹는 커피보다 쓰고 텁텁함이 훨씬 강하게 밀려옴</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>더딘 다이어트 효능 체감 — 체지방 연소나 감량 면에서 가시적인 생리적 효과를 실질적으로 느끼기 어려움</t>
-        </is>
-      </c>
+          <t>단맛 없는 생강 맛 호불호 — 단맛이 전혀 없어 원액 그대로 마시기엔 맛이 다소 아쉬움</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
     </row>
     <row r="11" ht="38" customHeight="1">
       <c r="B11" t="inlineStr">
         <is>
-          <t>홍삼/인삼</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -5506,49 +5579,53 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>[신혜선 PICK] 동국제약 면역엔 홍삼 필름 10매 10일분</t>
+          <t>[김종국 PICK] 익스트림 아르기닌 에너지온 2개입 2일분</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>익스트림</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>1,500원</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=610911096&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=987253277&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260805/X3lfEnRBZWFGAzpNcACh610911096_00_01X3lfEnRBZWFGAzpNcACh.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260422/eIhoZ9JSC5jbp33vSbZX987253277_00_01eIhoZ9JSC5jbp33vSbZX.jpg</t>
         </is>
       </c>
       <c r="I11" t="n">
         <v>4.8</v>
       </c>
       <c r="J11" t="n">
-        <v>48</v>
+        <v>757</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>간편한 신개념 필름 섭취 — 물을 머금지 않고 입에서 천천히 녹여 흡수시키는 방식이라 기력이 필요할 때 바로 활용함</t>
+          <t>즉각적인 에너지 충전 — 비타500 농축 맛으로 운동이나 업무 시 활력 충전에 도움됨</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>전반적인 몸의 활기 유지 — 가방에 두고 매일 녹여 취침 전후에 가볍게 먹어주면 생기 유지에 보탬이 됨</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr"/>
+          <t>편리한 2개입 소포장 — 급할 때 편의식으로 사서 바로 마시기 편함</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>부담 없는 가성비 가격 — 가격이 저렴하여 부담 없이 마실 수 있음</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>피할 수 없는 특유의 쓴맛 — 입안 점막에 닿으며 즉시 녹아내릴 때 홍삼 특유의 씁쓸한 약 맛이 곧바로 다소 강하게 올라옴</t>
+          <t>함량 대비 모호한 가격 — 아르기닌 함량 대비 엄청 저렴하지는 않게 느껴짐</t>
         </is>
       </c>
       <c r="O11" t="inlineStr"/>
@@ -5665,52 +5742,52 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>루테인/눈건강</t>
+          <t>혈행</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
           <t>기타/특수목적</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>기타/특수목적</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>비타민D</t>
-        </is>
-      </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>비타민C/항산화</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>홍삼/인삼</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
           <t>다이어트/체중관리</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>프로바이오틱스/유산균</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>다이어트/체중관리</t>
-        </is>
-      </c>
-      <c r="L3" s="3" t="inlineStr">
-        <is>
-          <t>홍삼/인삼</t>
         </is>
       </c>
     </row>
@@ -5727,47 +5804,47 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
+          <t>대웅제약</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>닥터블릿</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
           <t>동국제약</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>종근당건강</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>닥터블릿</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>동국제약</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>대웅제약</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>휴럼</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>이너뷰 바이 리튠</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>유한양행</t>
-        </is>
-      </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>셀트리온</t>
+          <t>홀베리</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>익스트림</t>
         </is>
       </c>
     </row>
@@ -5779,52 +5856,52 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>대웅제약 rTG오메가3 6캡슐 6일분</t>
+          <t>대웅제약 코엔자임Q10 6캡슐 6일분</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>[신혜선 PICK] 동국 마이팝 푸룬＆식이섬유</t>
+          <t>대웅제약 바나바잎 추출물 30정 30일분</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
+          <t>닥터블릿 멜라드림 30정 30일분</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>[산뜻한 상쾌함] [신혜선 PICK] 동국제약 프로폴리스 프레쉬볼 레몬＆민트 20캡슐 20일분</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>종근당건강 락토핏 골드</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
           <t>닥터블릿 푸응 7days 팻버닝 21캡슐</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>동국제약 비타민D 2000IU 40캡슐 40일분</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>대웅제약 비타민C 30정 30일분</t>
-        </is>
-      </c>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>휴럼 하루한알 6년근 고려 홍삼환 9환 9일분</t>
-        </is>
-      </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>LG생활건강 이너뷰 다이어트 가르시니아 10포</t>
+          <t>[옥수수수염＆호박] 동국제약 맛있는 센텔라 공주캔디 20정 20일분</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>유한양행 초코맛 생유산균 스틱 20포 20일분</t>
+          <t>대웅제약 비타민B 30정 30일분</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>[다영 PICK] 셀트리온 다이어트 한 잔 슬림 S 프레소 10포 5일분</t>
+          <t>홀베리 유기농 10포 레몬생강즙</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>[신혜선 PICK] 동국제약 면역엔 홍삼 필름 10매 10일분</t>
+          <t>[김종국 PICK] 익스트림 아르기닌 에너지온 2개입 2일분</t>
         </is>
       </c>
     </row>
@@ -5838,13 +5915,13 @@
         <v>4.8</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="G6" s="3" t="n">
         <v>4.8</v>
@@ -5853,10 +5930,10 @@
         <v>4.7</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="K6" s="3" t="n">
         <v>4.7</v>
@@ -5872,37 +5949,37 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>507</v>
+        <v>333</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>469</v>
+        <v>4757</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>2700</v>
+        <v>1708</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>1131</v>
+        <v>75</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>2682</v>
+        <v>1622</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>66</v>
+        <v>2701</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>1012</v>
+        <v>64</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>448</v>
+        <v>2197</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>2606</v>
+        <v>533</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="8" ht="60" customHeight="1">
+        <v>757</v>
+      </c>
+    </row>
+    <row r="8" ht="90" customHeight="1">
       <c r="B8" s="1" t="inlineStr">
         <is>
           <t>긍정리뷰</t>
@@ -5910,60 +5987,63 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>놀라운 가성비 혜택 — 다이소의 장점을 극대화한 가격 경쟁력으로 부담 없이 구매해 복용함
-휴대성 만점 미니 포장 — 가볍게 6일 단위로 개별 포장되어 타지로 갈 때 주머니나 파우치에 넣기 좋음</t>
+          <t>부담 없는 소량 포장 — 6일분 소용량으로 필요할 때 부담 없이 구매 가능함
+깔끔하고 간편한 휴대 — 소포장으로 나뉘어 있어 가방에 넣고 다니며 챙겨 먹기 편함</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>초고속 직빵 장 비우기 — 마신 지 약 한 시간 만에 아랫배에 신호가 와 장을 말끔히 청소함
-배앓이 없는 안전한 작용 — 인위적으로 강한 배 통증을 자극하지 않고 부드럽게 쾌변할 수 있도록 도와줌</t>
+          <t>다이소다운 착한 가성비 — 저렴한 가격으로 한 달 분량 혈당 관리 정제를 구매함
+식전 간편한 1정 복용 — 식사 전 한 알로 간편하게 혈당 스파이크 관리에 도움을 기대함</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>체지방 축적 방지 보조 — 과식이나 기름진 음식을 다량 먹었을 때 살이 찌지 않게 체지방 관리를 보조함
-상당한 대변 기능 향상 — 변비로 묵직했던 위장을 시원하게 비워주는 데 실질적 도움을 줌</t>
+          <t>빠른 입면과 숙면 유도 — 복용 후 20~30분 내로 졸음이 오며 중간에 깨지 않고 깊게 잠듦
+뛰어난 가성비 수면템 — 비싼 수면 보조제 대비 저렴한 가격으로 수면의 질을 개선함</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>매우 작은 초소형 캡슐 — 캡슐 크기가 획기적으로 작아 노약자도 부드럽고 수월하게 목으로 넘김
-가루 대비 부드러운 섭취 — 시거나 자극적인 맛의 비타민 분말과 달리 신맛이 전혀 느껴지지 않아 간편함</t>
+          <t>즉각적인 구강 상쾌함 — 작은 알을 터뜨리면 입안이 시원해지고 구취 관리에 도움됨
+가성비 좋은 데일리템 — 가격이 저렴하여 일상에서 부담 없이 구강 청결용으로 쓰기 좋음</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>우수한 극가성비 비타민 — 하루 일정 함량 이상의 필요한 성분을 매달 저렴하고 쉽게 공급할 수 있음
-느껴지는 피로 예방 효과 — 꾸준히 복용 시 아침 일과 진행 시 기력이 크게 처지는 것을 예방함</t>
+          <t>복부 가스 및 팽만 완화 — 배에 가스가 차는 증상을 줄여주고 편안한 장 환경에 도움됨
+부담 없는 저렴한 가격 — 다이소몰에서 저렴하게 구매할 수 있어 재구매 의사 높음</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>부드럽고 유연한 섭취 환 — 홍삼의 짙은 향이 지나치지 않아 입에서 가볍게 깨물어 간편히 복용할 수 있음
-순수 홍삼 위주의 안전 배합 — 체질에 안 맞을 수 있는 녹용이 빠지고 홍삼만 들어가 예민한 분도 안심하고 먹음</t>
+          <t>다이어트 체지방 관리 — 명절이나 단기 다이어트 시 체지방 관리 목적으로 섭취하기 좋음
+개별 포장의 휴대 편의 — 낱개 포장이라 휴대하기 간편하고 챙겨 먹기 수월함</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>식사 후 빠른 탄수 관리 — 식사 시 빵이나 면류를 대량 복용한 날 편리하게 물에 연하게 풀어 타 마시기 수월함</t>
+          <t>새콤달콤한 복숭아맛 — 달콤하고 상큼한 맛으로 간식처럼 거부감 없이 복용함
+붓기 관리 및 체감 효과 — 섭취 후 붓기 완화 효과를 비교적 빠르게 체감함</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>매력적인 진한 초콜릿향 — 기존 맛없는 영양제와 다르게 진한 카카오 맛이 퍼져 디저트 대용으로 훌륭함
-아이들이 좋아하는 대중성 — 부모가 보채지 않아도 편식하는 어린이가 먼저 스스로 찾아 섭취함</t>
+          <t>온 가족 데일리 비타민 — 온 가족이 함께 매일 꾸준히 복용하기에 적합함
+믿을 수 있는 제약사 — 대웅제약 브랜드 제품으로 신뢰하고 구매함</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>깔끔한 아메리카노 맛 대용 — 피로를 깨울 겸 에스프레소 느낌의 카페인 음료처럼 부담 없이 타 마시기 적절함</t>
+          <t>부담 없는 저렴한 가격 — 인터넷 판매가 대비 저렴한 가격으로 구매 만족도 높음
+무가당 건강 레몬생강 — 당분이 없어 따뜻한 물과 꿀에 타 먹기 좋음</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>간편한 신개념 필름 섭취 — 물을 머금지 않고 입에서 천천히 녹여 흡수시키는 방식이라 기력이 필요할 때 바로 활용함
-전반적인 몸의 활기 유지 — 가방에 두고 매일 녹여 취침 전후에 가볍게 먹어주면 생기 유지에 보탬이 됨</t>
+          <t>즉각적인 에너지 충전 — 비타500 농축 맛으로 운동이나 업무 시 활력 충전에 도움됨
+편리한 2개입 소포장 — 급할 때 편의식으로 사서 바로 마시기 편함
+부담 없는 가성비 가격 — 가격이 저렴하여 부담 없이 마실 수 있음</t>
         </is>
       </c>
     </row>
@@ -5974,38 +6054,31 @@
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr"/>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>지나치게 잦은 설사 유도 — 개인 위장 상태에 따라 너무 강력하게 작용하여 설사가 동반될 우려가 있음</t>
-        </is>
-      </c>
+      <c r="D9" s="3" t="inlineStr"/>
       <c r="E9" s="3" t="inlineStr"/>
-      <c r="F9" s="3" t="inlineStr"/>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>자극적인 민트 매운맛 — 민트 맛이 다소 강해 매운맛에 민감하면 자극적으로 느껴짐
+부족한 캡슐 내용물 — 캡슐 안 액상 내용물 용량이 적어 한 번에 2알을 복용하게 됨</t>
+        </is>
+      </c>
       <c r="G9" s="3" t="inlineStr"/>
-      <c r="H9" s="3" t="inlineStr">
-        <is>
-          <t>다소 미미한 홍삼의 잔향 — 전통적인 홍삼 특유의 깊은 한방 향이나 기운이 약하게 퍼지는 듯함</t>
-        </is>
-      </c>
+      <c r="H9" s="3" t="inlineStr"/>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>입에 남는 잔여 약 맛 — 간식처럼 가볍게 타 먹기 좋은 제형이나 미미하게 인위적인 제제 향이 입안에 남음</t>
-        </is>
-      </c>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t>일시적인 소화 이상 증세 — 체질이나 상태에 따라 가벼운 설사 증세 등 속이 다소 맞지 않는 경우가 있음</t>
-        </is>
-      </c>
+          <t>복숭아 알레르기 유발 — 복숭아 분말이 함유되어 복숭아 알레르기 유발 위험이 있음
+버전별 맛 선호도 차이 — 기존 초록색 제품에 비해 복숭아 맛이 덜 맛있게 느껴짐</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="inlineStr"/>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>다소 극단적으로 쓴 풍미 — 약재가 결합하여 평소 먹는 커피보다 쓰고 텁텁함이 훨씬 강하게 밀려옴
-더딘 다이어트 효능 체감 — 체지방 연소나 감량 면에서 가시적인 생리적 효과를 실질적으로 느끼기 어려움</t>
+          <t>단맛 없는 생강 맛 호불호 — 단맛이 전혀 없어 원액 그대로 마시기엔 맛이 다소 아쉬움</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>피할 수 없는 특유의 쓴맛 — 입안 점막에 닿으며 즉시 녹아내릴 때 홍삼 특유의 씁쓸한 약 맛이 곧바로 다소 강하게 올라옴</t>
+          <t>함량 대비 모호한 가격 — 아르기닌 함량 대비 엄청 저렴하지는 않게 느껴짐</t>
         </is>
       </c>
     </row>
@@ -6022,7 +6095,7 @@
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>2,000원</t>
+          <t>3,000원</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
@@ -6047,22 +6120,22 @@
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
+          <t>3,000원</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>3,000원</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
           <t>5,000원</t>
         </is>
       </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>5,000원</t>
-        </is>
-      </c>
-      <c r="K10" s="3" t="inlineStr">
-        <is>
-          <t>2,000원</t>
-        </is>
-      </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>1,500원</t>
         </is>
       </c>
     </row>
@@ -6241,7 +6314,7 @@
     <row r="2" ht="38" customHeight="1">
       <c r="B2" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>프로바이오틱스/유산균</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -6249,35 +6322,31 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>[4일추가증정] 그린몬스터 다이어트 쾌변쑥/체지방쏙 기획세트</t>
+          <t>덴프스 덴마크 유산균이야기 우먼 2개월분(질유산균) + 철분 헤모케어 3포 증정</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>그린몬스터</t>
+          <t>덴프스</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>9,900원</t>
+          <t>31,900원</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000199923&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=1</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000202658&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=1</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0019/A00000019992347ko.jpg?l=ko</t>
-        </is>
-      </c>
-      <c r="I2" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="J2" t="n">
-        <v>2460</v>
-      </c>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020265829ko.jpg?l=ko</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
@@ -6288,7 +6357,7 @@
     <row r="3" ht="38" customHeight="1">
       <c r="B3" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -6296,38 +6365,46 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>[저분자] 빌드 프리미엄 테프 발효 효소 30포 (1개월분)</t>
+          <t>[한선화 PICK] 프로뉴트리션 듀얼플랜 다이어트 유산균 14포</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>빌드</t>
+          <t>프로뉴트리션</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>18,900원</t>
+          <t>39,800원</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000219379&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=2</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000205496&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=2</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0021/A00000021937922ko.jpg?l=ko</t>
-        </is>
-      </c>
-      <c r="I3" t="n">
-        <v>5</v>
-      </c>
-      <c r="J3" t="n">
-        <v>20322</v>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020549614ko.jpg?l=ko</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>다이어트와 장 건강 관리 — 체지방 감소와 장 건강을 동시에 관리할 수 있어 다이어트 시 복용하기 좋음</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>상큼한 요거트맛 제형 — 상큼한 요거트 맛으로 하루 한 포 거부감 없이 섭취 가능함</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>신뢰도 높은 특허 배합 — 약사 개발 및 식약처 기능성 인정을 받아 믿고 섭취함</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
@@ -6343,31 +6420,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>[감자숭이 기획] 멜라메이트 구미/로우슈가/버라이어티팩 구미 20/40/50구미</t>
+          <t>[곽민경 PICK] 생활약속 기분전환 알파플러스 10포 (+1포 증정기획)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>멜라메이트</t>
+          <t>생활약속</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>16,900원</t>
+          <t>19,000원</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000223554&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=3</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000180121&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=3</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0022/A00000022355477ko.jpg?l=ko</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0018/A00000018012128ko.jpg?l=ko</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J4" t="n">
+        <v>16868</v>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
@@ -6378,7 +6459,7 @@
     <row r="5" ht="38" customHeight="1">
       <c r="B5" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -6386,39 +6467,55 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>[딥트3일/남규리Pick]남규리의 바른 효소 리셋 8포</t>
+          <t>[9월 올영픽/산리오콜라보] CJ 바이오코어 유산균 3종 (피부/다이어트/500억) (+산리오 러기지택)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>딥트3일</t>
+          <t>바이오코어유산균</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>16,000원</t>
+          <t>12,900원</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000211396&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=4</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000200143&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=4</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0021/A00000021139617ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020014347ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="J5" t="n">
-        <v>811</v>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+        <v>12654</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>배 아픔 없는 배변 활동 — 복통이나 가스 참 없이 편안하게 화장실을 가게 됨</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>귀여운 산리오 굿즈 증정 — 산리오 러기지택 사은품 구성으로 구매 만족도가 큼</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>하루 한 포 간편 루틴 — 바쁜 일상에서 하루 한 포로 장 건강을 챙길 수 있음</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>다소 큰 알약 크기 — 기존 제품 대비 캡슐 크기가 조금 큰 편임</t>
+        </is>
+      </c>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
     </row>
@@ -6433,35 +6530,31 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>[9월 올영픽/산리오콜라보] CJ 바이오코어 유산균 3종 (피부/다이어트/500억) (+산리오 러기지택)</t>
+          <t>[9월 올영픽] 콜레올로지 컷 다이어트 유산균 14캡슐 (+마이멜로디 카라비너) (10일분) / 20캡슐</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>바이오코어유산균</t>
+          <t>푸드올로지</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>12,900원</t>
+          <t>18,700원</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000200143&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=5</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000229934&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=5</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020014347ko.jpg?l=ko</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="J6" t="n">
-        <v>12647</v>
-      </c>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0022/A00000022993425ko.jpg?l=ko</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
@@ -6472,7 +6565,7 @@
     <row r="7" ht="38" customHeight="1">
       <c r="B7" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -6480,54 +6573,42 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>[추성훈 PICK] 헬스헬퍼 맥스컷 프로 크롬 60캡슐 (10일분)</t>
+          <t>콜레올로지 PRO 600mg*30정/60정/120정 (15/30/60일분)</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>헬스헬퍼</t>
+          <t>푸드올로지</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>17,960원</t>
+          <t>17,900원</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000237482&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=6</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000175634&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=6</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0023/A00000023748215ko.png?l=ko</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="J7" t="n">
-        <v>1363</v>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>가파른 살크업 방지 작용 — 부득이하게 몸져누워 폭식하고 잘 때 몸무게 급상승을 막는 용도로 적격임</t>
-        </is>
-      </c>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0017/A00000017563488ko.jpg?l=ko</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>목구멍 안쪽에 달라붙는 촉감 — 식후에 물과 넘길 때 매끄럽게 흡수되지 않고 가끔 목젖 부근에 밀착되는 느낌을 받음</t>
-        </is>
-      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
     </row>
     <row r="8" ht="38" customHeight="1">
       <c r="B8" t="inlineStr">
         <is>
-          <t>프로바이오틱스/유산균</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -6535,27 +6616,27 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>덴프스 덴마크 유산균이야기 우먼 2개월분(질유산균) + 철분 헤모케어 3포 증정</t>
+          <t>[딥트3일/남규리PICK]남규리의 바른 효소 리셋 8포</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>덴프스</t>
+          <t>딥트3일</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>31,900원</t>
+          <t>16,000원</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000202658&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=7</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000211396&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=7</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020265829ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0021/A00000021139617ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -6605,7 +6686,7 @@
         <v>4.9</v>
       </c>
       <c r="J9" t="n">
-        <v>28128</v>
+        <v>28129</v>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
@@ -6617,7 +6698,7 @@
     <row r="10" ht="38" customHeight="1">
       <c r="B10" t="inlineStr">
         <is>
-          <t>멀티비타민/종합비타민</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -6625,42 +6706,46 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>[9월 올영픽/김우빈PICK] 아임비타 멀티비타민 이뮨샷 12입 (+포차코 메쉬백) (12일분)</t>
+          <t>[저분자] 빌드 프리미엄 테프 발효 효소 30포 (1개월분)</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>아임비타</t>
+          <t>빌드</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>25,900원</t>
+          <t>18,900원</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000249166&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=9</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000219379&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=9</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A000000249166123ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0021/A00000021937922ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
-          <t>귀엽고 알찬 전용 메쉬백 — 귀여운 포차코 캐릭터가 있는 다용도 물 빠짐 메쉬 가방을 같이 줘서 실용성 최고임</t>
+          <t>고소한 인절미 맛 효소 — 곡물 효소 특유의 쿰쿰함 없이 고소하고 맛있게 섭취 가능함</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>맛있고 진한 비타민 음료 — 삼키기 적당한 형태의 정제와 함께 아래 농축된 진한 상큼 음료의 조합으로 맛있게 복용함</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr"/>
+          <t>부드러운 미세 분말 입자 — 입자가 매우 고와 가루날림 없이 편안하게 넘어감</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>탄수화물 식후 체중 관리 — 빵이나 면 등 탄수화물 섭취 후 소화 및 체중 조절에 도움됨</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
@@ -6668,7 +6753,7 @@
     <row r="11" ht="38" customHeight="1">
       <c r="B11" t="inlineStr">
         <is>
-          <t>비타민D</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -6676,27 +6761,27 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>닥터언 비타민D 30캡슐 (1개월분) (온)</t>
+          <t>콜레올로지 컷팅 젤리 레몬/키위/석류 10+2+2포 기획 외</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>닥터언</t>
+          <t>푸드올로지</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>4,000원</t>
+          <t>18,800원</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000247071&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=10</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000183645&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=10</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024707102ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0018/A00000018364589ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -6819,52 +6904,52 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
+          <t>프로바이오틱스/유산균</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
           <t>다이어트/체중관리</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>기타/특수목적</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
         <is>
           <t>기타/특수목적</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>멀티비타민/종합비타민</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
         <is>
           <t>기타/특수목적</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="L3" s="3" t="inlineStr">
         <is>
           <t>다이어트/체중관리</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>프로바이오틱스/유산균</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>멀티비타민/종합비타민</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>멀티비타민/종합비타민</t>
-        </is>
-      </c>
-      <c r="L3" s="3" t="inlineStr">
-        <is>
-          <t>비타민D</t>
         </is>
       </c>
     </row>
@@ -6876,52 +6961,52 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>그린몬스터</t>
+          <t>덴프스</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
+          <t>프로뉴트리션</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>생활약속</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>바이오코어유산균</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>푸드올로지</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>푸드올로지</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>딥트3일</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>오쏘몰</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
           <t>빌드</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>멜라메이트</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>딥트3일</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>바이오코어유산균</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>헬스헬퍼</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>덴프스</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>오쏘몰</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>아임비타</t>
-        </is>
-      </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>닥터언</t>
+          <t>푸드올로지</t>
         </is>
       </c>
     </row>
@@ -6933,52 +7018,52 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>[4일추가증정] 그린몬스터 다이어트 쾌변쑥/체지방쏙 기획세트</t>
+          <t>덴프스 덴마크 유산균이야기 우먼 2개월분(질유산균) + 철분 헤모케어 3포 증정</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
+          <t>[한선화 PICK] 프로뉴트리션 듀얼플랜 다이어트 유산균 14포</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>[곽민경 PICK] 생활약속 기분전환 알파플러스 10포 (+1포 증정기획)</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>[9월 올영픽/산리오콜라보] CJ 바이오코어 유산균 3종 (피부/다이어트/500억) (+산리오 러기지택)</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>[9월 올영픽] 콜레올로지 컷 다이어트 유산균 14캡슐 (+마이멜로디 카라비너) (10일분) / 20캡슐</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>콜레올로지 PRO 600mg*30정/60정/120정 (15/30/60일분)</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>[딥트3일/남규리PICK]남규리의 바른 효소 리셋 8포</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>오쏘몰 이뮨 멀티비타민&amp;미네랄 7입 (1주일분)</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
           <t>[저분자] 빌드 프리미엄 테프 발효 효소 30포 (1개월분)</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>[감자숭이 기획] 멜라메이트 구미/로우슈가/버라이어티팩 구미 20/40/50구미</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>[딥트3일/남규리Pick]남규리의 바른 효소 리셋 8포</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>[9월 올영픽/산리오콜라보] CJ 바이오코어 유산균 3종 (피부/다이어트/500억) (+산리오 러기지택)</t>
-        </is>
-      </c>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>[추성훈 PICK] 헬스헬퍼 맥스컷 프로 크롬 60캡슐 (10일분)</t>
-        </is>
-      </c>
-      <c r="I5" s="3" t="inlineStr">
-        <is>
-          <t>덴프스 덴마크 유산균이야기 우먼 2개월분(질유산균) + 철분 헤모케어 3포 증정</t>
-        </is>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>오쏘몰 이뮨 멀티비타민&amp;미네랄 7입 (1주일분)</t>
-        </is>
-      </c>
-      <c r="K5" s="3" t="inlineStr">
-        <is>
-          <t>[9월 올영픽/김우빈PICK] 아임비타 멀티비타민 이뮨샷 12입 (+포차코 메쉬백) (12일분)</t>
-        </is>
-      </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>닥터언 비타민D 30캡슐 (1개월분) (온)</t>
+          <t>콜레올로지 컷팅 젤리 레몬/키위/석류 10+2+2포 기획 외</t>
         </is>
       </c>
     </row>
@@ -6988,22 +7073,16 @@
           <t>평점</t>
         </is>
       </c>
-      <c r="C6" s="3" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="D6" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="E6" s="3" t="inlineStr"/>
+      <c r="C6" s="3" t="inlineStr"/>
+      <c r="D6" s="3" t="inlineStr"/>
+      <c r="E6" s="3" t="n">
+        <v>4.8</v>
+      </c>
       <c r="F6" s="3" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="G6" s="3" t="n">
         <v>4.8</v>
       </c>
-      <c r="H6" s="3" t="n">
-        <v>4.8</v>
-      </c>
+      <c r="G6" s="3" t="inlineStr"/>
+      <c r="H6" s="3" t="inlineStr"/>
       <c r="I6" s="3" t="inlineStr"/>
       <c r="J6" s="3" t="n">
         <v>4.9</v>
@@ -7017,51 +7096,54 @@
           <t>리뷰수</t>
         </is>
       </c>
-      <c r="C7" s="3" t="n">
-        <v>2460</v>
-      </c>
-      <c r="D7" s="3" t="n">
-        <v>20322</v>
-      </c>
-      <c r="E7" s="3" t="inlineStr"/>
+      <c r="C7" s="3" t="inlineStr"/>
+      <c r="D7" s="3" t="inlineStr"/>
+      <c r="E7" s="3" t="n">
+        <v>16868</v>
+      </c>
       <c r="F7" s="3" t="n">
-        <v>811</v>
-      </c>
-      <c r="G7" s="3" t="n">
-        <v>12647</v>
-      </c>
-      <c r="H7" s="3" t="n">
-        <v>1363</v>
-      </c>
+        <v>12654</v>
+      </c>
+      <c r="G7" s="3" t="inlineStr"/>
+      <c r="H7" s="3" t="inlineStr"/>
       <c r="I7" s="3" t="inlineStr"/>
       <c r="J7" s="3" t="n">
-        <v>28128</v>
+        <v>28129</v>
       </c>
       <c r="K7" s="3" t="inlineStr"/>
       <c r="L7" s="3" t="inlineStr"/>
     </row>
-    <row r="8" ht="60" customHeight="1">
+    <row r="8" ht="90" customHeight="1">
       <c r="B8" s="1" t="inlineStr">
         <is>
           <t>긍정리뷰</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr"/>
-      <c r="D8" s="3" t="inlineStr"/>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>다이어트와 장 건강 관리 — 체지방 감소와 장 건강을 동시에 관리할 수 있어 다이어트 시 복용하기 좋음
+상큼한 요거트맛 제형 — 상큼한 요거트 맛으로 하루 한 포 거부감 없이 섭취 가능함
+신뢰도 높은 특허 배합 — 약사 개발 및 식약처 기능성 인정을 받아 믿고 섭취함</t>
+        </is>
+      </c>
       <c r="E8" s="3" t="inlineStr"/>
-      <c r="F8" s="3" t="inlineStr"/>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>배 아픔 없는 배변 활동 — 복통이나 가스 참 없이 편안하게 화장실을 가게 됨
+귀여운 산리오 굿즈 증정 — 산리오 러기지택 사은품 구성으로 구매 만족도가 큼
+하루 한 포 간편 루틴 — 바쁜 일상에서 하루 한 포로 장 건강을 챙길 수 있음</t>
+        </is>
+      </c>
       <c r="G8" s="3" t="inlineStr"/>
-      <c r="H8" s="3" t="inlineStr">
-        <is>
-          <t>가파른 살크업 방지 작용 — 부득이하게 몸져누워 폭식하고 잘 때 몸무게 급상승을 막는 용도로 적격임</t>
-        </is>
-      </c>
+      <c r="H8" s="3" t="inlineStr"/>
       <c r="I8" s="3" t="inlineStr"/>
       <c r="J8" s="3" t="inlineStr"/>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>귀엽고 알찬 전용 메쉬백 — 귀여운 포차코 캐릭터가 있는 다용도 물 빠짐 메쉬 가방을 같이 줘서 실용성 최고임
-맛있고 진한 비타민 음료 — 삼키기 적당한 형태의 정제와 함께 아래 농축된 진한 상큼 음료의 조합으로 맛있게 복용함</t>
+          <t>고소한 인절미 맛 효소 — 곡물 효소 특유의 쿰쿰함 없이 고소하고 맛있게 섭취 가능함
+부드러운 미세 분말 입자 — 입자가 매우 고와 가루날림 없이 편안하게 넘어감
+탄수화물 식후 체중 관리 — 빵이나 면 등 탄수화물 섭취 후 소화 및 체중 조절에 도움됨</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr"/>
@@ -7075,13 +7157,13 @@
       <c r="C9" s="3" t="inlineStr"/>
       <c r="D9" s="3" t="inlineStr"/>
       <c r="E9" s="3" t="inlineStr"/>
-      <c r="F9" s="3" t="inlineStr"/>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>다소 큰 알약 크기 — 기존 제품 대비 캡슐 크기가 조금 큰 편임</t>
+        </is>
+      </c>
       <c r="G9" s="3" t="inlineStr"/>
-      <c r="H9" s="3" t="inlineStr">
-        <is>
-          <t>목구멍 안쪽에 달라붙는 촉감 — 식후에 물과 넘길 때 매끄럽게 흡수되지 않고 가끔 목젖 부근에 밀착되는 느낌을 받음</t>
-        </is>
-      </c>
+      <c r="H9" s="3" t="inlineStr"/>
       <c r="I9" s="3" t="inlineStr"/>
       <c r="J9" s="3" t="inlineStr"/>
       <c r="K9" s="3" t="inlineStr"/>
@@ -7095,52 +7177,52 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>9,900원</t>
+          <t>31,900원</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
+          <t>39,800원</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>19,000원</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>12,900원</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>18,700원</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>17,900원</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>16,000원</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>38,000원</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
           <t>18,900원</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t>16,900원</t>
-        </is>
-      </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>16,000원</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t>12,900원</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>17,960원</t>
-        </is>
-      </c>
-      <c r="I10" s="3" t="inlineStr">
-        <is>
-          <t>31,900원</t>
-        </is>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>38,000원</t>
-        </is>
-      </c>
-      <c r="K10" s="3" t="inlineStr">
-        <is>
-          <t>25,900원</t>
-        </is>
-      </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>4,000원</t>
+          <t>18,800원</t>
         </is>
       </c>
     </row>
@@ -7228,7 +7310,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7266,51 +7348,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>멀티비타민/종합비타민</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C2" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="D2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C3" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="D3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E3" t="n">
         <v>2</v>
       </c>
       <c r="F3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>멀티비타민/종합비타민</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -7320,32 +7402,32 @@
         <v>22.5</v>
       </c>
       <c r="D4" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>홍삼/인삼</t>
+          <t>피부/미용</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C5" t="n">
-        <v>7.5</v>
+        <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -7354,20 +7436,20 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>피부/미용</t>
+          <t>혈행</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C6" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="D6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -7376,20 +7458,20 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>비타민D</t>
+          <t>프로바이오틱스/유산균</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
         <v>1</v>
@@ -7398,66 +7480,22 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>프로바이오틱스/유산균</t>
+          <t>홍삼/인삼</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C8" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="D8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" t="n">
         <v>0</v>
       </c>
-      <c r="E8" t="n">
-        <v>1</v>
-      </c>
       <c r="F8" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>비타민C/항산화</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" t="n">
-        <v>1</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>루테인/눈건강</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>1</v>
-      </c>
-      <c r="C10" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" t="n">
-        <v>1</v>
-      </c>
-      <c r="F10" t="n">
         <v>0</v>
       </c>
     </row>
